--- a/reference/listing_sikbom.xlsx
+++ b/reference/listing_sikbom.xlsx
@@ -3769,7 +3769,7 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>17300</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="T27" s="7" t="inlineStr">
@@ -27645,7 +27645,7 @@
       </c>
       <c r="S181" s="7" t="inlineStr">
         <is>
-          <t>59300</t>
+          <t>64500</t>
         </is>
       </c>
       <c r="T181" s="7" t="inlineStr">
@@ -29361,7 +29361,7 @@
       </c>
       <c r="S192" s="7" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="T192" s="7" t="inlineStr">
@@ -66653,7 +66653,7 @@
       </c>
       <c r="S431" s="7" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="T431" s="7" t="inlineStr">

--- a/reference/listing_sikbom.xlsx
+++ b/reference/listing_sikbom.xlsx
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="Q38" s="7" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="T38" s="7" t="inlineStr">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="P76" s="7" t="inlineStr">
         <is>
-          <t>165400</t>
+          <t>151800</t>
         </is>
       </c>
       <c r="Q76" s="7" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="S76" s="7" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>122100</t>
         </is>
       </c>
       <c r="T76" s="7" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="P136" s="7" t="inlineStr">
         <is>
-          <t>70900</t>
+          <t>63800</t>
         </is>
       </c>
       <c r="Q136" s="7" t="inlineStr">
@@ -20637,7 +20637,7 @@
       </c>
       <c r="S136" s="7" t="inlineStr">
         <is>
-          <t>48900</t>
+          <t>52200</t>
         </is>
       </c>
       <c r="T136" s="7" t="inlineStr">
@@ -28410,7 +28410,7 @@
       </c>
       <c r="P186" s="7" t="inlineStr">
         <is>
-          <t>68900</t>
+          <t>63500</t>
         </is>
       </c>
       <c r="Q186" s="7" t="inlineStr">
@@ -28425,7 +28425,7 @@
       </c>
       <c r="S186" s="7" t="inlineStr">
         <is>
-          <t>47500</t>
+          <t>49500</t>
         </is>
       </c>
       <c r="T186" s="7" t="inlineStr">
@@ -46982,7 +46982,7 @@
       </c>
       <c r="P305" s="7" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>15500</t>
         </is>
       </c>
       <c r="Q305" s="7" t="inlineStr">
@@ -46997,7 +46997,7 @@
       </c>
       <c r="S305" s="7" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="T305" s="7" t="inlineStr">
@@ -52598,7 +52598,7 @@
       </c>
       <c r="P341" s="7" t="inlineStr">
         <is>
-          <t>39000</t>
+          <t>41000</t>
         </is>
       </c>
       <c r="Q341" s="7" t="inlineStr">
@@ -52613,7 +52613,7 @@
       </c>
       <c r="S341" s="7" t="inlineStr">
         <is>
-          <t>26900</t>
+          <t>31600</t>
         </is>
       </c>
       <c r="T341" s="7" t="inlineStr">
@@ -72254,7 +72254,7 @@
       </c>
       <c r="P467" s="7" t="inlineStr">
         <is>
-          <t>122200</t>
+          <t>136800</t>
         </is>
       </c>
       <c r="Q467" s="7" t="inlineStr">
@@ -72269,7 +72269,7 @@
       </c>
       <c r="S467" s="7" t="inlineStr">
         <is>
-          <t>88300</t>
+          <t>108600</t>
         </is>
       </c>
       <c r="T467" s="7" t="inlineStr">
@@ -81146,7 +81146,7 @@
       </c>
       <c r="P524" s="7" t="inlineStr">
         <is>
-          <t>54800</t>
+          <t>49900</t>
         </is>
       </c>
       <c r="Q524" s="7" t="inlineStr">
@@ -81161,7 +81161,7 @@
       </c>
       <c r="S524" s="7" t="inlineStr">
         <is>
-          <t>37800</t>
+          <t>41500</t>
         </is>
       </c>
       <c r="T524" s="7" t="inlineStr">

--- a/reference/listing_sikbom.xlsx
+++ b/reference/listing_sikbom.xlsx
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>24200</t>
         </is>
       </c>
       <c r="Q52" s="7" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>17600</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="T52" s="7" t="inlineStr">
@@ -65866,7 +65866,7 @@
       </c>
       <c r="P422" s="7" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="Q422" s="7" t="inlineStr">
@@ -65881,7 +65881,7 @@
       </c>
       <c r="S422" s="7" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="T422" s="7" t="inlineStr">
@@ -66334,7 +66334,7 @@
       </c>
       <c r="P425" s="7" t="inlineStr">
         <is>
-          <t>21600</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="Q425" s="7" t="inlineStr">
@@ -66349,7 +66349,7 @@
       </c>
       <c r="S425" s="7" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="T425" s="7" t="inlineStr">

--- a/reference/listing_sikbom.xlsx
+++ b/reference/listing_sikbom.xlsx
@@ -41370,7 +41370,7 @@
       </c>
       <c r="P265" s="7" t="inlineStr">
         <is>
-          <t>11600</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="Q265" s="7" t="inlineStr">
@@ -41385,7 +41385,7 @@
       </c>
       <c r="S265" s="7" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="T265" s="7" t="inlineStr">
@@ -57758,7 +57758,7 @@
       </c>
       <c r="P370" s="7" t="inlineStr">
         <is>
-          <t>30300</t>
+          <t>27300</t>
         </is>
       </c>
       <c r="Q370" s="7" t="inlineStr">
@@ -57773,7 +57773,7 @@
       </c>
       <c r="S370" s="7" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>22000</t>
         </is>
       </c>
       <c r="T370" s="7" t="inlineStr">
@@ -91610,7 +91610,7 @@
       </c>
       <c r="P587" s="7" t="inlineStr">
         <is>
-          <t>41300</t>
+          <t>37000</t>
         </is>
       </c>
       <c r="Q587" s="7" t="inlineStr">
@@ -91625,7 +91625,7 @@
       </c>
       <c r="S587" s="7" t="inlineStr">
         <is>
-          <t>28500</t>
+          <t>30800</t>
         </is>
       </c>
       <c r="T587" s="7" t="inlineStr">

--- a/reference/listing_sikbom.xlsx
+++ b/reference/listing_sikbom.xlsx
@@ -90537,7 +90537,7 @@
       </c>
       <c r="S580" s="7" t="inlineStr">
         <is>
-          <t>18200</t>
+          <t>17700</t>
         </is>
       </c>
       <c r="T580" s="7" t="inlineStr">

--- a/reference/listing_sikbom.xlsx
+++ b/reference/listing_sikbom.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="T8" s="7" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>21900</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="T13" s="7" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="T16" s="7" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="T24" s="7" t="inlineStr">

--- a/reference/listing_sikbom.xlsx
+++ b/reference/listing_sikbom.xlsx
@@ -12854,7 +12854,7 @@
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="S81" s="7" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="T81" s="7" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>15100</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="T83" s="7" t="inlineStr">
@@ -17566,7 +17566,7 @@
       </c>
       <c r="P112" s="7" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="Q112" s="7" t="inlineStr">
@@ -17581,7 +17581,7 @@
       </c>
       <c r="S112" s="7" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="T112" s="7" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="P171" s="7" t="inlineStr">
         <is>
-          <t>51200</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="Q171" s="7" t="inlineStr">
@@ -26741,7 +26741,7 @@
       </c>
       <c r="S171" s="7" t="inlineStr">
         <is>
-          <t>34600</t>
+          <t>35600</t>
         </is>
       </c>
       <c r="T171" s="7" t="inlineStr">
@@ -45110,7 +45110,7 @@
       </c>
       <c r="P289" s="7" t="inlineStr">
         <is>
-          <t>23500</t>
+          <t>21700</t>
         </is>
       </c>
       <c r="Q289" s="7" t="inlineStr">
@@ -45125,7 +45125,7 @@
       </c>
       <c r="S289" s="7" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="T289" s="7" t="inlineStr">
@@ -61498,7 +61498,7 @@
       </c>
       <c r="P394" s="7" t="inlineStr">
         <is>
-          <t>21600</t>
+          <t>20100</t>
         </is>
       </c>
       <c r="Q394" s="7" t="inlineStr">
@@ -61513,7 +61513,7 @@
       </c>
       <c r="S394" s="7" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="T394" s="7" t="inlineStr">
@@ -62278,7 +62278,7 @@
       </c>
       <c r="P399" s="7" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="Q399" s="7" t="inlineStr">
@@ -62293,7 +62293,7 @@
       </c>
       <c r="S399" s="7" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="T399" s="7" t="inlineStr">
@@ -62434,7 +62434,7 @@
       </c>
       <c r="P400" s="7" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>21500</t>
         </is>
       </c>
       <c r="Q400" s="7" t="inlineStr">
@@ -62449,7 +62449,7 @@
       </c>
       <c r="S400" s="7" t="inlineStr">
         <is>
-          <t>16100</t>
+          <t>16700</t>
         </is>
       </c>
       <c r="T400" s="7" t="inlineStr">
@@ -67582,7 +67582,7 @@
       </c>
       <c r="P433" s="7" t="inlineStr">
         <is>
-          <t>17300</t>
+          <t>15600</t>
         </is>
       </c>
       <c r="Q433" s="7" t="inlineStr">
@@ -67597,7 +67597,7 @@
       </c>
       <c r="S433" s="7" t="inlineStr">
         <is>
-          <t>11900</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="T433" s="7" t="inlineStr">
@@ -73042,7 +73042,7 @@
       </c>
       <c r="P468" s="7" t="inlineStr">
         <is>
-          <t>22200</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="Q468" s="7" t="inlineStr">
@@ -73057,7 +73057,7 @@
       </c>
       <c r="S468" s="7" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>16600</t>
         </is>
       </c>
       <c r="T468" s="7" t="inlineStr">
@@ -81310,7 +81310,7 @@
       </c>
       <c r="P521" s="7" t="inlineStr">
         <is>
-          <t>29900</t>
+          <t>26400</t>
         </is>
       </c>
       <c r="Q521" s="7" t="inlineStr">
@@ -81325,7 +81325,7 @@
       </c>
       <c r="S521" s="7" t="inlineStr">
         <is>
-          <t>20600</t>
+          <t>21300</t>
         </is>
       </c>
       <c r="T521" s="7" t="inlineStr">
@@ -82870,7 +82870,7 @@
       </c>
       <c r="P531" s="7" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="Q531" s="7" t="inlineStr">
@@ -82885,7 +82885,7 @@
       </c>
       <c r="S531" s="7" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>10700</t>
         </is>
       </c>
       <c r="T531" s="7" t="inlineStr">
@@ -83962,7 +83962,7 @@
       </c>
       <c r="P538" s="7" t="inlineStr">
         <is>
-          <t>22800</t>
+          <t>19800</t>
         </is>
       </c>
       <c r="Q538" s="7" t="inlineStr">
@@ -83977,7 +83977,7 @@
       </c>
       <c r="S538" s="7" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="T538" s="7" t="inlineStr">
@@ -88798,7 +88798,7 @@
       </c>
       <c r="P569" s="7" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="Q569" s="7" t="inlineStr">
@@ -88813,7 +88813,7 @@
       </c>
       <c r="S569" s="7" t="inlineStr">
         <is>
-          <t>17300</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="T569" s="7" t="inlineStr">

--- a/reference/listing_sikbom.xlsx
+++ b/reference/listing_sikbom.xlsx
@@ -9818,7 +9818,7 @@
       </c>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>27130</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="Q62" s="7" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>21700</t>
+          <t>25700</t>
         </is>
       </c>
       <c r="T62" s="7" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>27130</t>
+          <t>33300</t>
         </is>
       </c>
       <c r="Q63" s="7" t="inlineStr">
@@ -10005,7 +10005,7 @@
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>21700</t>
+          <t>25700</t>
         </is>
       </c>
       <c r="T63" s="7" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>26000</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="Q64" s="7" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="S64" s="7" t="inlineStr">
         <is>
-          <t>20800</t>
+          <t>25700</t>
         </is>
       </c>
       <c r="T64" s="7" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="P171" s="7" t="inlineStr">
         <is>
-          <t>45100</t>
+          <t>44200</t>
         </is>
       </c>
       <c r="Q171" s="7" t="inlineStr">
@@ -26741,7 +26741,7 @@
       </c>
       <c r="S171" s="7" t="inlineStr">
         <is>
-          <t>35600</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="T171" s="7" t="inlineStr">
@@ -83182,7 +83182,7 @@
       </c>
       <c r="P533" s="7" t="inlineStr">
         <is>
-          <t>24900</t>
+          <t>22300</t>
         </is>
       </c>
       <c r="Q533" s="7" t="inlineStr">
@@ -83197,7 +83197,7 @@
       </c>
       <c r="S533" s="7" t="inlineStr">
         <is>
-          <t>17200</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="T533" s="7" t="inlineStr">
@@ -85366,7 +85366,7 @@
       </c>
       <c r="P547" s="7" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="Q547" s="7" t="inlineStr">
@@ -85381,7 +85381,7 @@
       </c>
       <c r="S547" s="7" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="T547" s="7" t="inlineStr">
@@ -87862,7 +87862,7 @@
       </c>
       <c r="P563" s="7" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>23200</t>
         </is>
       </c>
       <c r="Q563" s="7" t="inlineStr">
@@ -87877,7 +87877,7 @@
       </c>
       <c r="S563" s="7" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="T563" s="7" t="inlineStr">
@@ -88174,7 +88174,7 @@
       </c>
       <c r="P565" s="7" t="inlineStr">
         <is>
-          <t>22300</t>
+          <t>22400</t>
         </is>
       </c>
       <c r="Q565" s="7" t="inlineStr">
@@ -88189,7 +88189,7 @@
       </c>
       <c r="S565" s="7" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="T565" s="7" t="inlineStr">

--- a/reference/listing_sikbom.xlsx
+++ b/reference/listing_sikbom.xlsx
@@ -23142,7 +23142,7 @@
       </c>
       <c r="P148" s="7" t="inlineStr">
         <is>
-          <t>106000</t>
+          <t>91300</t>
         </is>
       </c>
       <c r="Q148" s="7" t="inlineStr">
@@ -23157,7 +23157,7 @@
       </c>
       <c r="S148" s="7" t="inlineStr">
         <is>
-          <t>85500</t>
+          <t>75700</t>
         </is>
       </c>
       <c r="T148" s="7" t="inlineStr">
@@ -23454,7 +23454,7 @@
       </c>
       <c r="P150" s="7" t="inlineStr">
         <is>
-          <t>40900</t>
+          <t>35800</t>
         </is>
       </c>
       <c r="Q150" s="7" t="inlineStr">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="S150" s="7" t="inlineStr">
         <is>
-          <t>28200</t>
+          <t>27900</t>
         </is>
       </c>
       <c r="T150" s="7" t="inlineStr">
@@ -31398,7 +31398,7 @@
       </c>
       <c r="P201" s="7" t="inlineStr">
         <is>
-          <t>47600</t>
+          <t>36200</t>
         </is>
       </c>
       <c r="Q201" s="7" t="inlineStr">
@@ -31413,7 +31413,7 @@
       </c>
       <c r="S201" s="7" t="inlineStr">
         <is>
-          <t>32800</t>
+          <t>29400</t>
         </is>
       </c>
       <c r="T201" s="7" t="inlineStr">
@@ -32178,7 +32178,7 @@
       </c>
       <c r="P206" s="7" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="Q206" s="7" t="inlineStr">
@@ -32193,7 +32193,7 @@
       </c>
       <c r="S206" s="7" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="T206" s="7" t="inlineStr">
@@ -32334,7 +32334,7 @@
       </c>
       <c r="P207" s="7" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="Q207" s="7" t="inlineStr">
@@ -32349,7 +32349,7 @@
       </c>
       <c r="S207" s="7" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="T207" s="7" t="inlineStr">
@@ -32646,7 +32646,7 @@
       </c>
       <c r="P209" s="7" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="Q209" s="7" t="inlineStr">
@@ -32661,7 +32661,7 @@
       </c>
       <c r="S209" s="7" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="T209" s="7" t="inlineStr">
@@ -33738,7 +33738,7 @@
       </c>
       <c r="P216" s="7" t="inlineStr">
         <is>
-          <t>30600</t>
+          <t>24300</t>
         </is>
       </c>
       <c r="Q216" s="7" t="inlineStr">
@@ -33753,7 +33753,7 @@
       </c>
       <c r="S216" s="7" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="T216" s="7" t="inlineStr">
@@ -34050,7 +34050,7 @@
       </c>
       <c r="P218" s="7" t="inlineStr">
         <is>
-          <t>22500</t>
+          <t>21900</t>
         </is>
       </c>
       <c r="Q218" s="7" t="inlineStr">
@@ -34065,7 +34065,7 @@
       </c>
       <c r="S218" s="7" t="inlineStr">
         <is>
-          <t>17300</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="T218" s="7" t="inlineStr">
@@ -46214,7 +46214,7 @@
       </c>
       <c r="P296" s="7" t="inlineStr">
         <is>
-          <t>178100</t>
+          <t>136400</t>
         </is>
       </c>
       <c r="Q296" s="7" t="inlineStr">
@@ -46229,7 +46229,7 @@
       </c>
       <c r="S296" s="7" t="inlineStr">
         <is>
-          <t>122800</t>
+          <t>111000</t>
         </is>
       </c>
       <c r="T296" s="7" t="inlineStr">
@@ -62126,7 +62126,7 @@
       </c>
       <c r="P398" s="7" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>17200</t>
         </is>
       </c>
       <c r="Q398" s="7" t="inlineStr">
@@ -62141,7 +62141,7 @@
       </c>
       <c r="S398" s="7" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="T398" s="7" t="inlineStr">
@@ -63530,7 +63530,7 @@
       </c>
       <c r="P407" s="7" t="inlineStr">
         <is>
-          <t>116100</t>
+          <t>92100</t>
         </is>
       </c>
       <c r="Q407" s="7" t="inlineStr">
@@ -63545,7 +63545,7 @@
       </c>
       <c r="S407" s="7" t="inlineStr">
         <is>
-          <t>80100</t>
+          <t>74700</t>
         </is>
       </c>
       <c r="T407" s="7" t="inlineStr">
@@ -70394,7 +70394,7 @@
       </c>
       <c r="P451" s="7" t="inlineStr">
         <is>
-          <t>18700</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="Q451" s="7" t="inlineStr">
@@ -70409,7 +70409,7 @@
       </c>
       <c r="S451" s="7" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="T451" s="7" t="inlineStr">
@@ -74918,7 +74918,7 @@
       </c>
       <c r="P480" s="7" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="Q480" s="7" t="inlineStr">
@@ -74933,7 +74933,7 @@
       </c>
       <c r="S480" s="7" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="T480" s="7" t="inlineStr">
@@ -78974,7 +78974,7 @@
       </c>
       <c r="P506" s="7" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>16300</t>
         </is>
       </c>
       <c r="Q506" s="7" t="inlineStr">
@@ -78989,7 +78989,7 @@
       </c>
       <c r="S506" s="7" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="T506" s="7" t="inlineStr">
@@ -92390,7 +92390,7 @@
       </c>
       <c r="P592" s="7" t="inlineStr">
         <is>
-          <t>34500</t>
+          <t>28500</t>
         </is>
       </c>
       <c r="Q592" s="7" t="inlineStr">
@@ -92405,7 +92405,7 @@
       </c>
       <c r="S592" s="7" t="inlineStr">
         <is>
-          <t>23800</t>
+          <t>23500</t>
         </is>
       </c>
       <c r="T592" s="7" t="inlineStr">
@@ -92546,7 +92546,7 @@
       </c>
       <c r="P593" s="7" t="inlineStr">
         <is>
-          <t>38300</t>
+          <t>33600</t>
         </is>
       </c>
       <c r="Q593" s="7" t="inlineStr">
@@ -92561,7 +92561,7 @@
       </c>
       <c r="S593" s="7" t="inlineStr">
         <is>
-          <t>26400</t>
+          <t>26100</t>
         </is>
       </c>
       <c r="T593" s="7" t="inlineStr">

--- a/reference/listing_sikbom.xlsx
+++ b/reference/listing_sikbom.xlsx
@@ -21094,7 +21094,7 @@
       </c>
       <c r="P135" s="7" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>33800</t>
         </is>
       </c>
       <c r="Q135" s="7" t="inlineStr">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="S135" s="7" t="inlineStr">
         <is>
-          <t>23100</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="T135" s="7" t="inlineStr">
@@ -22498,7 +22498,7 @@
       </c>
       <c r="P144" s="7" t="inlineStr">
         <is>
-          <t>33400</t>
+          <t>39100</t>
         </is>
       </c>
       <c r="Q144" s="7" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="S144" s="7" t="inlineStr">
         <is>
-          <t>25700</t>
+          <t>30600</t>
         </is>
       </c>
       <c r="T144" s="7" t="inlineStr">
@@ -36370,7 +36370,7 @@
       </c>
       <c r="P233" s="7" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="Q233" s="7" t="inlineStr">
@@ -36385,7 +36385,7 @@
       </c>
       <c r="S233" s="7" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>14400</t>
         </is>
       </c>
       <c r="T233" s="7" t="inlineStr">
@@ -61638,7 +61638,7 @@
       </c>
       <c r="P395" s="7" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="Q395" s="7" t="inlineStr">
@@ -61653,7 +61653,7 @@
       </c>
       <c r="S395" s="7" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="T395" s="7" t="inlineStr">
@@ -82386,7 +82386,7 @@
       </c>
       <c r="P528" s="7" t="inlineStr">
         <is>
-          <t>29100</t>
+          <t>25100</t>
         </is>
       </c>
       <c r="Q528" s="7" t="inlineStr">
@@ -82401,7 +82401,7 @@
       </c>
       <c r="S528" s="7" t="inlineStr">
         <is>
-          <t>20100</t>
+          <t>20800</t>
         </is>
       </c>
       <c r="T528" s="7" t="inlineStr">
@@ -83790,7 +83790,7 @@
       </c>
       <c r="P537" s="7" t="inlineStr">
         <is>
-          <t>114400</t>
+          <t>106600</t>
         </is>
       </c>
       <c r="Q537" s="7" t="inlineStr">
@@ -83805,7 +83805,7 @@
       </c>
       <c r="S537" s="7" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>86700</t>
         </is>
       </c>
       <c r="T537" s="7" t="inlineStr">

--- a/reference/listing_sikbom.xlsx
+++ b/reference/listing_sikbom.xlsx
@@ -17102,7 +17102,7 @@
       </c>
       <c r="P109" s="7" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="Q109" s="7" t="inlineStr">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="S109" s="7" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8550</t>
         </is>
       </c>
       <c r="T109" s="7" t="inlineStr">
@@ -22810,7 +22810,7 @@
       </c>
       <c r="P146" s="7" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>23500</t>
         </is>
       </c>
       <c r="Q146" s="7" t="inlineStr">
@@ -22825,7 +22825,7 @@
       </c>
       <c r="S146" s="7" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>18400</t>
         </is>
       </c>
       <c r="T146" s="7" t="inlineStr">
@@ -22966,7 +22966,7 @@
       </c>
       <c r="P147" s="7" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>20500</t>
         </is>
       </c>
       <c r="Q147" s="7" t="inlineStr">
@@ -22981,7 +22981,7 @@
       </c>
       <c r="S147" s="7" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>16100</t>
         </is>
       </c>
       <c r="T147" s="7" t="inlineStr">
@@ -27349,7 +27349,7 @@
       </c>
       <c r="S175" s="7" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>35300</t>
         </is>
       </c>
       <c r="T175" s="7" t="inlineStr">
@@ -37138,7 +37138,7 @@
       </c>
       <c r="P238" s="7" t="inlineStr">
         <is>
-          <t>235900</t>
+          <t>203000</t>
         </is>
       </c>
       <c r="Q238" s="7" t="inlineStr">
@@ -37153,7 +37153,7 @@
       </c>
       <c r="S238" s="7" t="inlineStr">
         <is>
-          <t>162700</t>
+          <t>168200</t>
         </is>
       </c>
       <c r="T238" s="7" t="inlineStr">
@@ -39162,7 +39162,7 @@
       </c>
       <c r="P251" s="7" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="Q251" s="7" t="inlineStr">
@@ -39177,7 +39177,7 @@
       </c>
       <c r="S251" s="7" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="T251" s="7" t="inlineStr">
@@ -40816,7 +40816,7 @@
       </c>
       <c r="B262" s="7" t="inlineStr">
         <is>
-          <t>PC003745</t>
+          <t>PC004180</t>
         </is>
       </c>
       <c r="C262" s="7" t="inlineStr">
@@ -73022,7 +73022,7 @@
       </c>
       <c r="P468" s="7" t="inlineStr">
         <is>
-          <t>21900</t>
+          <t>25700</t>
         </is>
       </c>
       <c r="Q468" s="7" t="inlineStr">
@@ -73037,7 +73037,7 @@
       </c>
       <c r="S468" s="7" t="inlineStr">
         <is>
-          <t>17600</t>
+          <t>21400</t>
         </is>
       </c>
       <c r="T468" s="7" t="inlineStr">
@@ -84098,7 +84098,7 @@
       </c>
       <c r="P539" s="7" t="inlineStr">
         <is>
-          <t>11700</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="Q539" s="7" t="inlineStr">
@@ -84113,7 +84113,7 @@
       </c>
       <c r="S539" s="7" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="T539" s="7" t="inlineStr">

--- a/reference/listing_sikbom.xlsx
+++ b/reference/listing_sikbom.xlsx
@@ -41034,7 +41034,7 @@
       </c>
       <c r="P263" s="7" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>14200</t>
         </is>
       </c>
       <c r="Q263" s="7" t="inlineStr">
@@ -41049,7 +41049,7 @@
       </c>
       <c r="S263" s="7" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="T263" s="7" t="inlineStr">
@@ -69434,7 +69434,7 @@
       </c>
       <c r="P445" s="7" t="inlineStr">
         <is>
-          <t>33900</t>
+          <t>29400</t>
         </is>
       </c>
       <c r="Q445" s="7" t="inlineStr">
@@ -69449,7 +69449,7 @@
       </c>
       <c r="S445" s="7" t="inlineStr">
         <is>
-          <t>23400</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="T445" s="7" t="inlineStr">
